--- a/space-battleship/config_excel/charge.xlsx
+++ b/space-battleship/config_excel/charge.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="charge" sheetId="6" r:id="rId1"/>
@@ -1065,11 +1060,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="13.3796296296296" customWidth="1"/>
-    <col min="3" max="3" width="34.4444444444444" customWidth="1"/>
-    <col min="14" max="14" width="12.8888888888889"/>
+    <col min="1" max="1" width="13.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="34.4416666666667" customWidth="1"/>
+    <col min="14" max="14" width="12.8916666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1188,7 +1183,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1209,7 +1204,7 @@
         <v>1.3</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1223,7 +1218,7 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1244,7 +1239,7 @@
         <v>1.3</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1279,7 +1274,7 @@
         <v>1.3</v>
       </c>
       <c r="K6">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/charge.xlsx
+++ b/space-battleship/config_excel/charge.xlsx
@@ -1204,7 +1204,7 @@
         <v>1.3</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1239,7 +1239,7 @@
         <v>1.3</v>
       </c>
       <c r="K5">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1274,7 +1274,7 @@
         <v>1.3</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/charge.xlsx
+++ b/space-battleship/config_excel/charge.xlsx
@@ -1077,9 +1077,6 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
@@ -1112,9 +1109,6 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
@@ -1147,9 +1141,6 @@
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
@@ -1182,9 +1173,6 @@
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
       <c r="E4">
         <v>2</v>
       </c>
@@ -1217,9 +1205,6 @@
       <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
       <c r="E5">
         <v>2</v>
       </c>
@@ -1251,9 +1236,6 @@
       </c>
       <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
